--- a/Excel/DialogTable.xlsx
+++ b/Excel/DialogTable.xlsx
@@ -8,13 +8,13 @@
       <x15ac:absPath xmlns:x15ac="http://schemas.microsoft.com/office/spreadsheetml/2010/11/ac" url="D:\Github\MillenniumOfCultivation\Excel\"/>
     </mc:Choice>
   </mc:AlternateContent>
-  <xr:revisionPtr revIDLastSave="0" documentId="13_ncr:1_{78B9A675-9991-4AB2-9F59-F18F23316047}" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{00000000-0000-0000-0000-000000000000}"/>
+  <xr:revisionPtr revIDLastSave="0" documentId="13_ncr:1_{7DA4FBFD-BC80-4250-B043-27407937BA8C}" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{00000000-0000-0000-0000-000000000000}"/>
   <bookViews>
-    <workbookView xWindow="38290" yWindow="-110" windowWidth="38620" windowHeight="21100" xr2:uid="{00000000-000D-0000-FFFF-FFFF00000000}"/>
+    <workbookView xWindow="8820" yWindow="1630" windowWidth="28800" windowHeight="15410" activeTab="1" xr2:uid="{00000000-000D-0000-FFFF-FFFF00000000}"/>
   </bookViews>
   <sheets>
-    <sheet name="@DialogTable" sheetId="1" r:id="rId1"/>
-    <sheet name="@PortraitTable" sheetId="2" r:id="rId2"/>
+    <sheet name="#DialogTable" sheetId="1" r:id="rId1"/>
+    <sheet name="#PortraitTable" sheetId="2" r:id="rId2"/>
   </sheets>
   <calcPr calcId="162913"/>
   <extLst>
